--- a/daily_matches/job_matches_2026-10-14.xlsx
+++ b/daily_matches/job_matches_2026-10-14.xlsx
@@ -456,42 +456,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Systems Architect - TS/SCI w/ Poly required</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Leading Path Consulting</t>
+          <t>Friant &amp; Associates</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Warrenton, VA, USA USA</t>
+          <t>San Leandro, CA, USA USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>28.9</v>
+        <v>26.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, BigQuery, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51b2560066a45e46</t>
+          <t>https://www.indeed.com/viewjob?jk=d4182938ad6c7715</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer III - Enterprise Architecture</t>
+          <t>Software Engineer II - Enterprise Architecture</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -519,164 +519,164 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06dafa8e9aa46f13</t>
+          <t>https://www.indeed.com/viewjob?jk=f41e5aaffae63b67</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Store AI Agent - Onshore Data Engineer (Python, Pytorch, NodeJS)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>21.1</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD</t>
+          <t>Data Scientist, RAG, PyTorch, Data Lake, MLflow, Docker, Kubernetes, CI/CD, Git, Databricks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf7d5b09dec217c</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d863cb3c38f06b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>SS - Onshore Data Engineer (Python, Pytorch)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Surescripts</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, BigQuery, Docker, Jenkins, Terraform, Git, BigQuery</t>
+          <t>Data Scientist, RAG, PyTorch, Data Lake, MLflow, Docker, Kubernetes, CI/CD, Git, Databricks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4483784feda6d19</t>
+          <t>https://www.indeed.com/viewjob?jk=1804ca13c879a613</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Specialist, Yield Management - GTM Data Engineer</t>
+          <t>Software Engineer 2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dearborn, MI, USA USA</t>
+          <t>Louisville, KY, USA USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Dataflow, Apache Airflow, CI/CD, Git, Snowflake, BigQuery, Tableau</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f50e110d31ed36a</t>
+          <t>https://www.indeed.com/viewjob?jk=6352c20c3850230b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Full-Stack Senior Developers</t>
+          <t>Agentic AI Cloud Development Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Natoli Engineering</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Saint Charles, MO, USA USA</t>
+          <t>San Juan, PR, USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL</t>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9e928d074bdf699</t>
+          <t>https://www.indeed.com/viewjob?jk=76a6ee6846be4448</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Health Data Modeler</t>
+          <t>Senior Full Stack .NET Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RCR Technology</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Irving, TX, USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -684,69 +684,69 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Cortex, Synapse, Data Lake, Git, Snowflake, Databricks, Tableau, Power BI</t>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=339b2689dab59d45</t>
+          <t>https://www.indeed.com/viewjob?jk=324384e3bfc85ae8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DevOps / Infrastructure Engineer</t>
+          <t>AWS Trainium / AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Alchemy Cloud</t>
+          <t>Capgemini Engineering</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, MySQL</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Gemini, PyTorch, EC2, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fb1e7413def7791</t>
+          <t>https://www.indeed.com/viewjob?jk=969caa7818d5488a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior AI Engineer – Voice &amp; Conversational AI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tower Loan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Flowood, MS, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -754,252 +754,252 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, Python</t>
+          <t>Generative AI, RAG, Gemini, S3, EC2, CI/CD, Jenkins, Git, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8523e9b248098040</t>
+          <t>https://www.indeed.com/viewjob?jk=3f6a4e0ed209eb9d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer 2 – Java, Generative AI, RAG &amp; Cloud Engineering</t>
+          <t>Senior HCM Data Scientist - Remote</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CHS Corporate</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hopkins, MN, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, scikit-learn, Keras, spaCy, NLTK, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdfcf5a045e444da</t>
+          <t>https://www.indeed.com/viewjob?jk=db64d642995cb43a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Business Intelligence Data Modeler Engineer Senior I</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Kirkland &amp; Ellis</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Irving, TX, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Apache Airflow, CI/CD, GitHub Actions, Git, Databricks, Tableau, Power BI, Python</t>
+          <t>RAG, Synapse, Data Lake, Snowflake, Databricks, PySpark, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=954d7871d42f0836</t>
+          <t>https://www.indeed.com/viewjob?jk=3a79945a69d44134</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Agentic AI</t>
+          <t>Kubernetes (K8S) / HPC Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Autodesk</t>
+          <t>Capgemini Engineering</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TX, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Kinesis, FastAPI, Docker, CI/CD, Jenkins, GitHub Actions, Git, Kafka, Python</t>
+          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, AKS, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83bf744cfc9ec983</t>
+          <t>https://www.indeed.com/viewjob?jk=323b413fb629f4d4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Engineer Data II</t>
+          <t>Sr. Data Scientist, Rental - Google Analytics</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IGT</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, Glue, Apache Airflow, CI/CD, Git, Databricks, Python, SQL</t>
+          <t>Data Scientist, RAG, BigQuery, Git, BigQuery, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0da8f75cf9c2b540</t>
+          <t>https://www.indeed.com/viewjob?jk=cacaf0ee979ec87f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Camera Vision Software Engineer</t>
+          <t>Data &amp; AI Strategist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Brooks Automation</t>
+          <t>Slalom Consulting</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Fremont, CA, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, OpenCV, Docker, Kubernetes, Git, NoSQL, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, Git, Snowflake, Databricks, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=756895f100a868c0</t>
+          <t>https://www.indeed.com/viewjob?jk=093aa6e04b777116</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Data Science</t>
+          <t>DevSecOps Engineer - VA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>National Grid</t>
+          <t>Connected Logistics</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Syracuse, NY, USA USA</t>
+          <t>Huntsville, AL, USA USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, GitHub Actions, Terraform, Git, Snowflake, PostgreSQL, Python, SQL</t>
+          <t>RAG, Azure ML, FastAPI, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f1008d3fb908fe1</t>
+          <t>https://www.indeed.com/viewjob?jk=e036edfd557c3af2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Enterprise Data Warehouse (EDW) ETL/Data Engineer</t>
+          <t>Senior Software Engineer: Back-end</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RCR Technology</t>
+          <t>LogicGate</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Synapse, Data Lake, CI/CD, Terraform, Snowflake, Databricks, PySpark, Python</t>
+          <t>RAG, Docker, CI/CD, Terraform, Git, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1009,199 +1009,199 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8800b92970b28dfb</t>
+          <t>https://www.indeed.com/viewjob?jk=b2201bc5edbb32a7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer II - Full Stack &amp; AI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, USA USA</t>
+          <t>O'Fallon, MO, USA USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, NoSQL, Python, SQL</t>
+          <t>Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f2fd64feb403af5</t>
+          <t>https://www.indeed.com/viewjob?jk=eadfe87c770bfddc</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marketing Data Engineer</t>
+          <t>Senior Software Engineer - Java Full Stack &amp; AI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Living Spaces</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>La Mirada, CA, USA USA</t>
+          <t>O'Fallon, MO, USA USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Dataflow, Git, BigQuery, Tableau, Power BI, Python, SQL, R</t>
+          <t>Copilot, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f01e86c7eb2733</t>
+          <t>https://www.indeed.com/viewjob?jk=7e59f1d190af6811</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>University of Maryland Global Campus</t>
+          <t>SJSU Research Foundation</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Adelphi, MD, USA USA</t>
+          <t>San Jose, CA, USA USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Redshift, Git, Databricks, Redshift, PySpark, Tableau, Python, SQL, R</t>
+          <t>RAG, Data Lake, Apache Airflow, Snowflake, Databricks, Tableau, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1eb27537b9273b0</t>
+          <t>https://www.indeed.com/viewjob?jk=e1de3366eafd1cc6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Jr. Cloud Automation Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fannie Mae</t>
+          <t>Qualified Health PBC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Reston, VA, USA USA</t>
+          <t>Palo Alto, CA, USA USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, CI/CD, Terraform, Git, NoSQL, Python, SQL, R</t>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Python, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c700c5ee304c350</t>
+          <t>https://www.indeed.com/viewjob?jk=ad5184141997c8ed</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Associate Software Engineer, AI Solutions</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cayuse</t>
+          <t>Qualified Health PBC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>Palo Alto, CA, USA USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Docker, CI/CD, Git, Snowflake, Python, SQL</t>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Python, R</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3c09c14f8f38705</t>
+          <t>https://www.indeed.com/viewjob?jk=39f90698eae0b7a0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Hardware Data Analyst - Remote</t>
+          <t>Development Operations Engineer II</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Aperia Technologies</t>
+          <t>University of Alabama</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Mateo, CA, USA USA</t>
+          <t>Tuscaloosa, AL, USA USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Redshift, Kinesis, Redshift, Tableau, Quicksight, Python, SQL</t>
+          <t>RAG, BigQuery, Docker, CI/CD, GitHub Actions, Terraform, Git, BigQuery, Python, R</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1219,32 +1219,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdfb0cd7e8eb714d</t>
+          <t>https://www.indeed.com/viewjob?jk=9713de64b8968966</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr Cloud Data and AI Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>University of Maryland Global Campus</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Adelphi, MD, USA USA</t>
+          <t>Charlotte, NC, USA USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Redshift, Git, Databricks, Redshift, PySpark, Tableau, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, RAG, Cortex, Git, Snowflake, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1254,59 +1254,59 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=705ae459e19365e9</t>
+          <t>https://www.indeed.com/viewjob?jk=dcb593a3c2a17eb4</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Development Operations Engineer II</t>
+          <t>Senior Scientist, Bioinformatics / Computational Biology</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>University of Alabama</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tuscaloosa, AL, USA USA</t>
+          <t>Cambridge, MA, USA USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Docker, CI/CD, GitHub Actions, Terraform, Git, BigQuery, Python, R</t>
+          <t>Data Scientist, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, scikit-learn, Git, Python, R</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebc985ecdf10dc8d</t>
+          <t>https://www.indeed.com/viewjob?jk=39c2ab20c887043e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, AI &amp; Data Systems</t>
+          <t>AI Developer, Implementations</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Blueprint Technologies</t>
+          <t>XiFin</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Redmond, WA, USA USA</t>
+          <t>San Diego, CA, USA USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1314,34 +1314,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Kafka, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a145733e0f5e9b51</t>
+          <t>https://www.indeed.com/viewjob?jk=d0358bb10a850936</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Development Engineer III - Java Stack</t>
+          <t>SW Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Irving, TX, USA USA</t>
+          <t>Austin, TX, USA USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1349,34 +1349,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Jenkins, Terraform, Git, NoSQL, SQL, R, Java, Scala</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a67dcea3b9163a</t>
+          <t>https://www.indeed.com/viewjob?jk=e1e53c31ec571504</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. DATA SCIENTIST</t>
+          <t>Software Engineer, Unsecured Installments</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Data and Analytic Solutions, Inc. (DAS)</t>
+          <t>Upstart</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1384,34 +1384,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Data Scientist, Redshift, Redshift, Tableau, Quicksight, MicroStrategy, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, CI/CD, Git, Python, R, Java, Scala, Optimization, A/B Testing</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e02f8f2aebb78d9</t>
+          <t>https://www.indeed.com/viewjob?jk=60ab8a28cb99ed62</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Software Engineer, Unsecured Installments</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Citco</t>
+          <t>Upstart</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Charlotte, NC, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1419,34 +1419,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
+          <t>Generative AI, RAG, CI/CD, Git, Python, R, Java, Scala, Optimization, A/B Testing</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5598a99fb5770b9d</t>
+          <t>https://www.indeed.com/viewjob?jk=cef2f1851b530e55</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Development Systems Engineer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>bp</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Houston, TX, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1454,42 +1454,42 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, CI/CD, Snowflake, Databricks, Python, SQL, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, Gemini, Docker, CI/CD, Git, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=671aed3088e72832</t>
+          <t>https://www.indeed.com/viewjob?jk=0550f74c602f7c40</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Vehicle Quality Engineering</t>
+          <t>A I animation and video, creating analysts / computer Science Software Developer.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Little hearts with God</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Warren, MI, USA USA</t>
+          <t>Northridge, CA, USA USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, Git, Databricks, Python, SQL, R, Scala</t>
+          <t>RAG, CI/CD, Git, MySQL, Python, SQL, R, Java, C++, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1499,24 +1499,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=744a3cb2d6fb585e</t>
+          <t>https://www.indeed.com/viewjob?jk=1f8d5e2becb41cac</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>AI Engineer, Forward Deployed (Copilot and Azure AI Foundry)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Boston Scientific</t>
+          <t>Collectiv LLC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Arden Hills, MN, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1524,34 +1524,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, Cortex, Snowflake, Python, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, CI/CD, Databricks, Power BI, Python, R</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=869f102503ed7c29</t>
+          <t>https://www.indeed.com/viewjob?jk=0692c331a9fac3d6</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Fraud Data Scientist</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>UMB Financial Corporation</t>
+          <t>Vantor</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kansas City, MO, USA USA</t>
+          <t>Herndon, VA, USA USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1559,34 +1559,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Snowflake, Tableau, Power BI, Python, SQL, R, A/B Testing</t>
+          <t>LangChain, RAG, GPT-4, Gemini, CI/CD, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fafd0195af073209</t>
+          <t>https://www.indeed.com/viewjob?jk=286566e8f0def12c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr Data Scientist- Wealth Management</t>
+          <t>Senior Machine Learning Engineer, New Verticals Agentic Foundations</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Columbus, OH, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Redshift, Git, Redshift, Python, SQL, R</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1604,24 +1604,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e87e5ea7f10f984e</t>
+          <t>https://www.indeed.com/viewjob?jk=ca7f7094a4526511</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Real Estate &amp; Facilities Data Analyst</t>
+          <t>Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Assurant</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Lebanon, NJ, USA USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1629,34 +1629,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Generative AI, Copilot, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, Glue, Git, Databricks, PySpark, Kafka, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd06040485183075</t>
+          <t>https://www.indeed.com/viewjob?jk=d3f6955e62075655</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Analyst II - Windreich Department of AI &amp; Human Health Research</t>
+          <t>Senior Software Engineer, Unsecured Installments</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>Upstart</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1664,34 +1664,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Git, Python, R</t>
+          <t>Generative AI, RAG, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=628eb4da8f6724fd</t>
+          <t>https://www.indeed.com/viewjob?jk=a701f4a3207b5b28</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer III, Data Platform Operations - Remote</t>
+          <t>Senior Software Engineer, Unsecured Installments</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Upstart</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1699,34 +1699,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, Glue, Data Lake, CI/CD, Snowflake, R, Scala</t>
+          <t>Generative AI, RAG, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbdb7a9bff45af0a</t>
+          <t>https://www.indeed.com/viewjob?jk=1c26556e48dbf5f1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sales Admin</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Zero Impact Solutions</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, USA USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1734,34 +1734,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa03512b87c00cd1</t>
+          <t>https://www.indeed.com/viewjob?jk=3ae5e8995c0d931d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer - SDET</t>
+          <t>Digital Manufacturing Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Capgemini Engineering</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austin, TX, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1769,34 +1769,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Generative AI, Copilot, Git, MySQL, Python, SQL, R, Java, C++</t>
+          <t>Generative AI, RAG, Gemini, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a29f5ec4d3d29510</t>
+          <t>https://www.indeed.com/viewjob?jk=6da93feec2e4e57b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Network Engineer, Product Software</t>
+          <t>Senior Associate - Automation Test Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Equinix</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dallas, TX, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1804,34 +1804,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
+          <t>Generative AI, RAG, CI/CD, Jenkins, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e2838ce3a6dadfd</t>
+          <t>https://www.indeed.com/viewjob?jk=07ce2616f236d446</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Databrick Data Engineering Consultant</t>
+          <t>Sales Admin</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SDG Group</t>
+          <t>Zero Impact Solutions</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Huntington Beach, CA, USA USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RAG, Snowflake, Databricks, PySpark, Python, SQL, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, Copilot, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1849,19 +1849,19 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e85cb5ceb58b2cf</t>
+          <t>https://www.indeed.com/viewjob?jk=8d7429b042d11903</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Quality Assurance Engineer - Cloud Web Platforms</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>TP-LINK</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1874,17 +1874,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5022aed5cea918da</t>
+          <t>https://www.indeed.com/viewjob?jk=f40f499b55ea4ea5</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-10-14.xlsx
+++ b/daily_matches/job_matches_2026-10-14.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,25 +456,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Systems Architect, SME</t>
+          <t>Senior Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VTG Defense</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, USA USA</t>
+          <t>Irving, TX, USA USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>28.9</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, BigQuery, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Copilot, Azure ML, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -484,67 +484,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74acab416de0ee2f</t>
+          <t>https://www.indeed.com/viewjob?jk=6f1d2c2073e68479</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Platform Engineer III</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
+          <t>RAG, TensorFlow, PyTorch, scikit-learn, OpenCV, EC2, Docker, Git, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f333eadf1da868ad</t>
+          <t>https://www.indeed.com/viewjob?jk=a1b38afdc998cd7a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior IT Programmer Analyst - Cloud DevOps</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>NextEra Energy</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dearborn, MI, USA USA</t>
+          <t>Juno Beach, FL, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, BigQuery, Dataflow, CI/CD, Git, BigQuery, Python</t>
+          <t>RAG, S3, Glue, Redshift, BigQuery, Dataflow, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -554,32 +554,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3efd9b4a5faab284</t>
+          <t>https://www.indeed.com/viewjob?jk=8bd9a034fcfe0278</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior AI Research Scientist – Foundation Models &amp; Agentic AI</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Intuitive (Intuitive Surgical)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>St. Louis, MO, USA USA</t>
+          <t>Sunnyvale, CA, USA USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, GPT-4, LLaMA, Copilot, Hugging Face, TensorFlow, PyTorch, Git</t>
+          <t>RAG, Docker, Kubernetes, Apache Airflow, CI/CD, Terraform, Git, Snowflake, Kafka, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -589,32 +589,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82a7371bf1effaa1</t>
+          <t>https://www.indeed.com/viewjob?jk=e6d31bded3f1a6c4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer - Materials Discovery Research Institute</t>
+          <t>Data Engineer - Mid-Level</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>UL Research Institutes</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Skokie, IL, USA USA</t>
+          <t>Rockville, MD, USA USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Terraform, Databricks, Python, SQL</t>
+          <t>RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Kafka, Hadoop, Matplotlib, Seaborn</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,24 +624,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f01d33f572b2baf0</t>
+          <t>https://www.indeed.com/viewjob?jk=f9ccf3f575e5d36b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Applied AI ML Associate</t>
+          <t>Media &amp; Marketing Data Scientist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Go Fish Digital</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -649,7 +649,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, MLflow, Python, R, Java, C++</t>
+          <t>Data Scientist, RAG, BigQuery, Git, BigQuery, Tableau, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,24 +659,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8876e930e0a115e8</t>
+          <t>https://www.indeed.com/viewjob?jk=b72b723aefa297b8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior .Net Developer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pennant Solutions Group</t>
+          <t>Rice University</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Richmond, VA, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -684,7 +684,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, S3, Data Lake, CI/CD, Git, SQL, R, Java</t>
+          <t>Data Scientist, RAG, FAISS, PyTorch, S3, Data Lake, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,24 +694,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38e5cb4fc3998bf6</t>
+          <t>https://www.indeed.com/viewjob?jk=21740eeeec1ddae4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4, DevOps</t>
+          <t>Java Developer with React</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Richmond, VA, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -719,7 +719,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94b9d21e2fce3783</t>
+          <t>https://www.indeed.com/viewjob?jk=e1346e9fc73ad3d4</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, USA USA</t>
+          <t>Tempe, AZ, USA USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -764,32 +764,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f316ed286d78567</t>
+          <t>https://www.indeed.com/viewjob?jk=023c8129fa3638ba</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Gen AI Platform Eng</t>
+          <t>Senior Software Engineer - Java Full Stack &amp; AI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dallas, TX, USA USA</t>
+          <t>O'Fallon, MO, USA USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Gemini, Prompt Engineering, Git, Python, R, Java, Scala</t>
+          <t>Copilot, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -799,32 +799,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d9c716ff0e8bc6</t>
+          <t>https://www.indeed.com/viewjob?jk=dbc5b57747195bb1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Engineer 4 (Gen AI Platform Services)</t>
+          <t>Data Engineer - AI, Agents, &amp; Context - Clinical (Sr. Associate)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Francisco, CA, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, PyTorch, Python, R, Java, C++, Scala, Optimization</t>
+          <t>AI Engineer, RAG, Pinecone, Power BI, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -834,32 +834,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01632af20c4fb04</t>
+          <t>https://www.indeed.com/viewjob?jk=7cbd8c0382f21dca</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Google - Knowledge Catalog -Engineer</t>
+          <t>Sr. Data Platform Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Alabama City, AL, USA USA</t>
+          <t>Munster, IN, USA USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, BigQuery, Git, BigQuery, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Data Lake, CI/CD, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -869,42 +869,147 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=296bcce9e557f414</t>
+          <t>https://www.indeed.com/viewjob?jk=c8f37e817406df46</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Laravel Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Nu Image Medical</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, USA USA</t>
+          <t>Franklin Lakes, NJ, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, CI/CD, Git, MySQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ed90148bac0d59f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Software Development Engineer I</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Clearwater Analytics (CWAN)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Boise, ID, USA USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>10</v>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, Jenkins, Git, MySQL, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f2e64040229a45cd</t>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, FastAPI, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=42cfa13e8904bd8a</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Sales Admin</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Zero Impact Solutions</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Irvine, CA, USA USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc94f6871e9e56b0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Business Analyst (Finance &amp; Sales)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Nebius</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>New York, NY, USA USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Snowflake, BigQuery, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76470b85174e6c57</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-10-14.xlsx
+++ b/daily_matches/job_matches_2026-10-14.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,25 +456,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Operations Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Irving, TX, USA USA</t>
+          <t>Conshohocken, PA, USA USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Copilot, Azure ML, MLflow, Docker, Kubernetes</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, LLaMA, Gemini, TensorFlow, PyTorch, scikit-learn, OpenCV</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -484,24 +484,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f1d2c2073e68479</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb909bf8906b9bc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Tampa, FL, USA USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -509,7 +509,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, scikit-learn, OpenCV, EC2, Docker, Git, MongoDB, NoSQL</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, S3, FastAPI, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -519,32 +519,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1b38afdc998cd7a</t>
+          <t>https://www.indeed.com/viewjob?jk=b29a69c2426b86b9</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior IT Programmer Analyst - Cloud DevOps</t>
+          <t>AI/ML Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NextEra Energy</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Juno Beach, FL, USA USA</t>
+          <t>Tampa, FL, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Redshift, BigQuery, Dataflow, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, S3, FastAPI, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -554,32 +554,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bd9a034fcfe0278</t>
+          <t>https://www.indeed.com/viewjob?jk=abe33be2b3728873</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior AI-Native Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Intuitive (Intuitive Surgical)</t>
+          <t>AT&amp;T</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, USA USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Apache Airflow, CI/CD, Terraform, Git, Snowflake, Kafka, Python</t>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, FastAPI, CI/CD, Git, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -589,32 +589,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6d31bded3f1a6c4</t>
+          <t>https://www.indeed.com/viewjob?jk=e0dc4dfa791cd07b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer - Mid-Level</t>
+          <t>Machine Learning Engineer I</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>NIKE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Rockville, MD, USA USA</t>
+          <t>Beaverton, OR, USA USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Kafka, Hadoop, Matplotlib, Seaborn</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, AWS SageMaker, FastAPI, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,32 +624,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9ccf3f575e5d36b</t>
+          <t>https://www.indeed.com/viewjob?jk=2afa70ba0967ae81</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Media &amp; Marketing Data Scientist</t>
+          <t>Cloud Data Engineer - AI Platform</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Go Fish Digital</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Charlotte, NC, USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Git, BigQuery, Tableau, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Glue, BigQuery, CI/CD, Terraform, Snowflake, BigQuery</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,32 +659,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b72b723aefa297b8</t>
+          <t>https://www.indeed.com/viewjob?jk=6af71823f4081c08</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rice University</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Bethesda, MD, USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, FAISS, PyTorch, S3, Data Lake, Docker, Kubernetes, Git, Python</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, scikit-learn, AWS SageMaker, Docker, Kubernetes, Kafka, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,32 +694,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21740eeeec1ddae4</t>
+          <t>https://www.indeed.com/viewjob?jk=2a322578c891277c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Java Developer with React</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Phoenix, AZ, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R</t>
+          <t>Generative AI, Gemini, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -729,32 +729,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1346e9fc73ad3d4</t>
+          <t>https://www.indeed.com/viewjob?jk=2ff76cb32130776d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior AI Research Scientist – Foundation Models &amp; Agentic AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tempe, AZ, USA USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, GPT-4, LLaMA, Copilot, Hugging Face, TensorFlow, PyTorch, Git</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git, Hadoop, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,32 +764,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=023c8129fa3638ba</t>
+          <t>https://www.indeed.com/viewjob?jk=9a4aaf4d33a99fad</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java Full Stack &amp; AI</t>
+          <t>Software Engineer III - Python/PySpark/Databricks/AWS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, USA USA</t>
+          <t>Wilmington, DE, USA USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R, Java</t>
+          <t>RAG, S3, Glue, CI/CD, Terraform, Snowflake, Databricks, PySpark, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -799,32 +799,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbc5b57747195bb1</t>
+          <t>https://www.indeed.com/viewjob?jk=a7261f813c68e65e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer - AI, Agents, &amp; Context - Clinical (Sr. Associate)</t>
+          <t>AI Software Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Kodexo Labs</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>San Diego, CA, USA USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Pinecone, Power BI, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>AI Engineer, RAG, Prompt Engineering, TensorFlow, PyTorch, scikit-learn, Docker, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -834,32 +834,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cbd8c0382f21dca</t>
+          <t>https://www.indeed.com/viewjob?jk=77769cff657e7411</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Data Platform Engineer</t>
+          <t>AI Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Munster, IN, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, CI/CD, Snowflake, Databricks, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, Copilot, CI/CD, Jenkins, Terraform, Git, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -869,32 +869,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8f37e817406df46</t>
+          <t>https://www.indeed.com/viewjob?jk=8b7efb07423344e6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Laravel Developer</t>
+          <t>Artificial Intelligence Operations Engineer (Full-time Hybrid, Morrisville, NC Based)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nu Image Medical</t>
+          <t>Alliance Health Plan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Franklin Lakes, NJ, USA USA</t>
+          <t>Morrisville, NC, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, CI/CD, Git, MySQL, SQL, R, Java, Scala, Optimization</t>
+          <t>AI Engineer, Data Scientist, Generative AI, Copilot, Docker, Kubernetes, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -904,32 +904,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed90148bac0d59f5</t>
+          <t>https://www.indeed.com/viewjob?jk=2166e4909af71406</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>Rice Engineering</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Boise, ID, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, FastAPI, Python, R, Java, Scala</t>
+          <t>Data Scientist, RAG, FAISS, PyTorch, S3, Data Lake, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -939,77 +939,462 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42cfa13e8904bd8a</t>
+          <t>https://www.indeed.com/viewjob?jk=de81ccc2964eab25</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sales Admin</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Zero Impact Solutions</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Irvine, CA, USA USA</t>
+          <t>Foster City, CA, USA USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc94f6871e9e56b0</t>
+          <t>https://www.indeed.com/viewjob?jk=7a2afb1e88ea9c47</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Business Analyst (Finance &amp; Sales)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nebius</t>
+          <t>Mass General Brigham</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Somerville, MA, USA USA</t>
         </is>
       </c>
       <c r="D17" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Data Lake, CI/CD, Git, Snowflake, PySpark, Kafka, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bcde93afa2a0a867</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Sr. Data Scientist I</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Zoro</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Chicago, IL, USA USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Docker, Kubernetes, Git, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec08ea91083b7af3</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Software Engineer (Back-end)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Engramme</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, USA USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>FastAPI, Docker, Kubernetes, CI/CD, Kafka, PostgreSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=88331719721cb534</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer - EAP/Employer (Remote)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Rula</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>USA USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, PostgreSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=844a36f434e961af</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Gen AI Engineers (Claude code, Codex, Cursor)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Accellor</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>San Jose, CA, USA USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, TensorFlow, PyTorch, Docker, Git, Python, R, C++, Optimization</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c6f887ef71e0d56a</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Pleasanton, CA, USA USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, CI/CD, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c48ccdcfb7b4fe57</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Clearwater Analytics (CWAN)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Chicago, IL, USA USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Kafka, Hadoop, Cassandra, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc746cb98ddc1200</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Data Engineer - Finance AI Solutions</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Brooklyn Park, MN, USA USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
         <v>10</v>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, Snowflake, BigQuery, Tableau, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=76470b85174e6c57</t>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, PySpark, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ef2140069fbbe73</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence Quality Engineer (Full-time Hybrid, Morrisville, NC Based)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Alliance Health Plan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Morrisville, NC, USA USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=28c9903641325277</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Engramme</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, USA USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=97ff25d3e80afc7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Data Scientist II - Risk Analytics, Governance &amp; Execution</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Truist</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, USA USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, Hadoop, NoSQL, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de12e664dcc9f48e</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CAI (Computer Aid, Inc.)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Miramar, FL, USA USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Generative AI, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d1d138ece3448e7</t>
         </is>
       </c>
     </row>
